--- a/main/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-28T09:43:11+00:00</t>
+    <t>2026-09-14T07:43:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T07:43:38+00:00</t>
+    <t>2026-10-01T07:35:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -574,7 +574,7 @@
     <t>Complétude de la dispensation</t>
   </si>
   <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-completude-dispensation-cisis|20260716085851</t>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-completude-dispensation-cisis|20260916095452</t>
   </si>
   <si>
     <t>Supply.code.nullFlavor</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-01T07:35:36+00:00</t>
+    <t>2026-10-14T13:15:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1003,8 +1003,8 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">value:$this}
-</t>
+    <t>profile:substanceAdministration}
+profile:act}</t>
   </si>
   <si>
     <t>Supply.entryRelationship:frReferenceItemPrescription</t>
@@ -1975,7 +1975,7 @@
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="73.9609375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="26.9921875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
@@ -12469,7 +12469,7 @@
         <v>81</v>
       </c>
       <c r="G104" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H104" t="s" s="2">
         <v>75</v>
@@ -14978,7 +14978,7 @@
         <v>81</v>
       </c>
       <c r="G129" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H129" t="s" s="2">
         <v>75</v>
@@ -18180,7 +18180,7 @@
         <v>81</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H161" t="s" s="2">
         <v>75</v>
@@ -20689,7 +20689,7 @@
         <v>81</v>
       </c>
       <c r="G186" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H186" t="s" s="2">
         <v>75</v>
@@ -23198,7 +23198,7 @@
         <v>81</v>
       </c>
       <c r="G211" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="H211" t="s" s="2">
         <v>75</v>

--- a/main/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T13:15:36+00:00</t>
+    <t>2026-10-15T09:41:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T09:41:25+00:00</t>
+    <t>2026-10-15T10:11:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T10:11:14+00:00</t>
+    <t>2026-10-15T11:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T11:51:04+00:00</t>
+    <t>2026-10-15T13:36:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T13:36:09+00:00</t>
+    <t>2026-10-15T15:46:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-15T15:46:20+00:00</t>
+    <t>2026-10-16T07:40:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T07:40:35+00:00</t>
+    <t>2026-10-16T08:34:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T08:34:24+00:00</t>
+    <t>2026-10-16T09:04:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
+++ b/main/ig/StructureDefinition-fr-cda-traitement-dispense.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T09:04:08+00:00</t>
+    <t>2026-10-16T11:38:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
